--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.63034863417354</v>
+        <v>2.7024316530532</v>
       </c>
       <c r="D2" t="n">
-        <v>17.79677749776506</v>
+        <v>2.891976343386823</v>
       </c>
       <c r="E2" t="n">
-        <v>17.20906390461844</v>
+        <v>2.796472884500497</v>
       </c>
       <c r="F2" t="n">
-        <v>13.60029279704789</v>
+        <v>2.210047579520283</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.95330718420718</v>
+        <v>1.779912417433667</v>
       </c>
       <c r="D3" t="n">
-        <v>38.12874918267241</v>
+        <v>6.195921742184266</v>
       </c>
       <c r="E3" t="n">
-        <v>17.20906390461844</v>
+        <v>2.796472884500497</v>
       </c>
       <c r="F3" t="n">
-        <v>13.60029279704789</v>
+        <v>2.210047579520283</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.607776787090142</v>
+        <v>0.911263727902148</v>
       </c>
       <c r="D4" t="n">
-        <v>39.32238548206352</v>
+        <v>6.389887640835322</v>
       </c>
       <c r="E4" t="n">
-        <v>17.20906390461844</v>
+        <v>2.796472884500497</v>
       </c>
       <c r="F4" t="n">
-        <v>13.60029279704789</v>
+        <v>2.210047579520283</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.43801112898095</v>
+        <v>8.846176808459406</v>
       </c>
       <c r="D5" t="n">
-        <v>57.40000509859704</v>
+        <v>9.32750082852202</v>
       </c>
       <c r="E5" t="n">
-        <v>17.20906390461844</v>
+        <v>2.796472884500497</v>
       </c>
       <c r="F5" t="n">
-        <v>13.60029279704789</v>
+        <v>2.210047579520283</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.26176187303701</v>
+        <v>4.105036304368515</v>
       </c>
       <c r="D6" t="n">
-        <v>24.99720182922026</v>
+        <v>4.062045297248292</v>
       </c>
       <c r="E6" t="n">
-        <v>17.20906390461844</v>
+        <v>2.796472884500497</v>
       </c>
       <c r="F6" t="n">
-        <v>13.60029279704789</v>
+        <v>2.210047579520283</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
